--- a/apps/web/public/templates/products-template.xlsx
+++ b/apps/web/public/templates/products-template.xlsx
@@ -13,40 +13,40 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
-    <t>sku</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>description</t>
-  </si>
-  <si>
-    <t>brand</t>
-  </si>
-  <si>
-    <t>ncm</t>
-  </si>
-  <si>
-    <t>gtin</t>
-  </si>
-  <si>
-    <t>weight</t>
-  </si>
-  <si>
-    <t>height</t>
-  </si>
-  <si>
-    <t>width</t>
-  </si>
-  <si>
-    <t>length</t>
-  </si>
-  <si>
-    <t>images</t>
-  </si>
-  <si>
-    <t>stock</t>
+    <t>SKU</t>
+  </si>
+  <si>
+    <t>Nome</t>
+  </si>
+  <si>
+    <t>Descrição</t>
+  </si>
+  <si>
+    <t>Marca</t>
+  </si>
+  <si>
+    <t>NCM</t>
+  </si>
+  <si>
+    <t>EAN</t>
+  </si>
+  <si>
+    <t>Peso (kg)</t>
+  </si>
+  <si>
+    <t>Altura (cm)</t>
+  </si>
+  <si>
+    <t>Largura (cm)</t>
+  </si>
+  <si>
+    <t>Comprimento (cm)</t>
+  </si>
+  <si>
+    <t>Imagens</t>
+  </si>
+  <si>
+    <t>Estoque</t>
   </si>
   <si>
     <t>PROD-001</t>
@@ -477,8 +477,10 @@
     <col min="4" max="4" width="18" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
-    <col min="7" max="9" width="10" customWidth="1"/>
-    <col min="10" max="10" width="12" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="9" max="9" width="13" customWidth="1"/>
+    <col min="10" max="10" width="17" customWidth="1"/>
     <col min="11" max="11" width="40" customWidth="1"/>
     <col min="12" max="12" width="10" customWidth="1"/>
   </cols>
